--- a/public/exports-from-60/29189811.xlsx
+++ b/public/exports-from-60/29189811.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -17239,12 +17239,12 @@
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896977</t>
+          <t xml:space="preserve">311896978</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M230" t="inlineStr">

--- a/public/exports-from-60/29189811.xlsx
+++ b/public/exports-from-60/29189811.xlsx
@@ -1031,11 +1031,11 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J14">
-        <v>341</v>
+        <v>227</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1091,26 +1091,26 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanegade 14</t>
+          <t xml:space="preserve">Kanalvej 1C</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">6870</t>
+          <t xml:space="preserve">6823</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">8290907</t>
+          <t xml:space="preserve">5076111</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J15">
-        <v>227</v>
+        <v>184</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1166,17 +1166,17 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kanalvej 1C</t>
+          <t xml:space="preserve">Kirkegade 5A</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">6823</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">5076111</t>
+          <t xml:space="preserve">5107615</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1185,7 +1185,7 @@
         </is>
       </c>
       <c r="J16">
-        <v>184</v>
+        <v>70</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkegade 5A</t>
+          <t xml:space="preserve">Kongsgaardsvej 24</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1251,16 +1251,16 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">5107615</t>
+          <t xml:space="preserve">736955, 5759230</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J17">
-        <v>70</v>
+        <v>176</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongsgaardsvej 24</t>
+          <t xml:space="preserve">Laboratorievej 14</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1326,16 +1326,16 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">736955, 5759230</t>
+          <t xml:space="preserve">736990, 5755769</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J18">
-        <v>176</v>
+        <v>77</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laboratorievej 14</t>
+          <t xml:space="preserve">Lerpøtvej 55</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1401,16 +1401,16 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">736990, 5755769</t>
+          <t xml:space="preserve">5756829</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J19">
-        <v>77</v>
+        <v>310</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1466,26 +1466,26 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lerpøtvej 55</t>
+          <t xml:space="preserve">Lærkevej 8</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6862</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">5756829</t>
+          <t xml:space="preserve">9212294</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J20">
-        <v>310</v>
+        <v>254</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J21">
@@ -1631,11 +1631,11 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J22">
-        <v>254</v>
+        <v>812</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1691,26 +1691,26 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lærkevej 8</t>
+          <t xml:space="preserve">Skadehøjvej 2A</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">6862</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">9212294</t>
+          <t xml:space="preserve">736999, 5757026</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J23">
-        <v>812</v>
+        <v>206</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1766,26 +1766,26 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skadehøjvej 2A</t>
+          <t xml:space="preserve">Skolegade 22</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6870</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">736999, 5757026</t>
+          <t xml:space="preserve">5081117</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J24">
-        <v>206</v>
+        <v>145</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1841,26 +1841,26 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 22</t>
+          <t xml:space="preserve">Skolevænget 12</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">6870</t>
+          <t xml:space="preserve">6840</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">5081117</t>
+          <t xml:space="preserve">8839667</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="J25">
-        <v>145</v>
+        <v>65</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1916,26 +1916,26 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 12</t>
+          <t xml:space="preserve">Strandvejen 415A</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">6840</t>
+          <t xml:space="preserve">6854</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">8839667</t>
+          <t xml:space="preserve">5091706</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J26">
-        <v>65</v>
+        <v>102</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1991,26 +1991,26 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandvejen 415A</t>
+          <t xml:space="preserve">Strandvejen 9A</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">6854</t>
+          <t xml:space="preserve">6840</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">5091706</t>
+          <t xml:space="preserve">8939771</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J27">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -2066,26 +2066,26 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandvejen 9A</t>
+          <t xml:space="preserve">Tirpitzvej 1</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">6840</t>
+          <t xml:space="preserve">6857</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">8939771</t>
+          <t xml:space="preserve">7867969</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J28">
-        <v>104</v>
+        <v>508</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -2141,26 +2141,26 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tirpitzvej 1</t>
+          <t xml:space="preserve">Vestergade 5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">6857</t>
+          <t xml:space="preserve">6870</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">7867969</t>
+          <t xml:space="preserve">5081928</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J29">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -2226,16 +2226,16 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">5081928</t>
+          <t xml:space="preserve">5081936</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J30">
-        <v>503</v>
+        <v>267</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">5081936</t>
+          <t xml:space="preserve">5081974</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J31">
-        <v>267</v>
+        <v>2228</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 5</t>
+          <t xml:space="preserve">Vestergade 7</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2376,16 +2376,16 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">5081974</t>
+          <t xml:space="preserve">7559492</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J32">
-        <v>2228</v>
+        <v>117</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 7</t>
+          <t xml:space="preserve">Vestergade 9</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2456,11 +2456,11 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J33">
-        <v>117</v>
+        <v>215</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2516,17 +2516,17 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 9</t>
+          <t xml:space="preserve">Vænget 51</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">6870</t>
+          <t xml:space="preserve">6818</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">7559492</t>
+          <t xml:space="preserve">7564727</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2535,7 +2535,7 @@
         </is>
       </c>
       <c r="J34">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2591,17 +2591,17 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vænget 51</t>
+          <t xml:space="preserve">Æblevej 7</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">6818</t>
+          <t xml:space="preserve">6852</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">7564727</t>
+          <t xml:space="preserve">5089553, 100197175</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2610,7 +2610,7 @@
         </is>
       </c>
       <c r="J35">
-        <v>222</v>
+        <v>77</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -2666,26 +2666,26 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Æblevej 7</t>
+          <t xml:space="preserve">Østparken 129B</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">6852</t>
+          <t xml:space="preserve">6840</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">5089553, 100197175</t>
+          <t xml:space="preserve">5088609</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J36">
-        <v>77</v>
+        <v>160</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -2741,17 +2741,17 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østparken 129B</t>
+          <t xml:space="preserve">Vesterled 50A</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">6840</t>
+          <t xml:space="preserve">6851</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">5088609</t>
+          <t xml:space="preserve">5094591</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2760,26 +2760,26 @@
         </is>
       </c>
       <c r="J37">
-        <v>160</v>
+        <v>1136</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
+          <t xml:space="preserve">200044645</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2021-01-21</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -2816,30 +2816,30 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vesterled 50A</t>
+          <t xml:space="preserve">Højgårdsparken 1</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">6851</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">5094591</t>
+          <t xml:space="preserve">1511503</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J38">
-        <v>1136</v>
+        <v>257</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t xml:space="preserve">200044645</t>
+          <t xml:space="preserve">200048960</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-01-21</t>
+          <t xml:space="preserve">2021-05-10</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -2891,50 +2891,50 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højgårdsparken 1</t>
+          <t xml:space="preserve">Tirpitzvej 1</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6857</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">1511503</t>
+          <t xml:space="preserve">7867969</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J39">
-        <v>257</v>
+        <v>2870</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t xml:space="preserve">200048960</t>
+          <t xml:space="preserve">311253609</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">FULDENDT P/S</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-05-10</t>
+          <t xml:space="preserve">2027-06-13</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -2966,40 +2966,40 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tirpitzvej 1</t>
+          <t xml:space="preserve">Rosenvænget 45</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">6857</t>
+          <t xml:space="preserve">6870</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">7867969</t>
+          <t xml:space="preserve">7767753</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J40">
-        <v>2870</v>
+        <v>1565</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311253609</t>
+          <t xml:space="preserve">311490959</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t xml:space="preserve">FULDENDT P/S</t>
+          <t xml:space="preserve">KEEN MILJØ &amp; ENERGIRÅDGIVNING ApS</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-13</t>
+          <t xml:space="preserve">2031-01-27</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3041,40 +3041,40 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenvænget 45</t>
+          <t xml:space="preserve">Ortenvej 64</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">6870</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">7767753</t>
+          <t xml:space="preserve">1511445</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J41">
-        <v>1565</v>
+        <v>9958</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311490959</t>
+          <t xml:space="preserve">311523520</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t xml:space="preserve">KEEN MILJØ &amp; ENERGIRÅDGIVNING ApS</t>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-27</t>
+          <t xml:space="preserve">2031-05-28</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3116,40 +3116,40 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ortenvej 64</t>
+          <t xml:space="preserve">Skovparken 5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6870</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">1511445</t>
+          <t xml:space="preserve">100177775</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J42">
-        <v>9958</v>
+        <v>3020</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311523520</t>
+          <t xml:space="preserve">311547428</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+          <t xml:space="preserve">Sandager Bygge- &amp; Energirådgivning ApS</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-28</t>
+          <t xml:space="preserve">2031-09-10</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3191,40 +3191,40 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovparken 5</t>
+          <t xml:space="preserve">Lærkevej 8</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">6870</t>
+          <t xml:space="preserve">6862</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">100177775</t>
+          <t xml:space="preserve">5080884</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J43">
-        <v>3020</v>
+        <v>5683</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547428</t>
+          <t xml:space="preserve">311686380</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sandager Bygge- &amp; Energirådgivning ApS</t>
+          <t xml:space="preserve">VITA Ingeniører</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-10</t>
+          <t xml:space="preserve">2033-06-08</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3266,17 +3266,17 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lærkevej 8</t>
+          <t xml:space="preserve">Lyngparken 1</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">6862</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">5080884</t>
+          <t xml:space="preserve">319097, 319098</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3285,21 +3285,21 @@
         </is>
       </c>
       <c r="J44">
-        <v>5683</v>
+        <v>3711</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686380</t>
+          <t xml:space="preserve">311711209</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t xml:space="preserve">VITA Ingeniører</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-08</t>
+          <t xml:space="preserve">2033-09-28</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3341,30 +3341,30 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngparken 1</t>
+          <t xml:space="preserve">Møllegårdsvej 9</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6862</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">319097, 319098</t>
+          <t xml:space="preserve">5079556</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J45">
-        <v>3711</v>
+        <v>917</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311711209</t>
+          <t xml:space="preserve">311730890</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-28</t>
+          <t xml:space="preserve">2033-12-21</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3416,30 +3416,30 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllegårdsvej 9</t>
+          <t xml:space="preserve">Egekrattet 7</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">6862</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">5079556</t>
+          <t xml:space="preserve">100545090</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J46">
-        <v>917</v>
+        <v>989</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311730890</t>
+          <t xml:space="preserve">311777304</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-21</t>
+          <t xml:space="preserve">2034-08-09</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egekrattet 7</t>
+          <t xml:space="preserve">Vesterbækvej 31</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3501,30 +3501,30 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">100545090</t>
+          <t xml:space="preserve">7427707</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J47">
-        <v>989</v>
+        <v>2030</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311777304</t>
+          <t xml:space="preserve">311832916</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-08-09</t>
+          <t xml:space="preserve">2035-05-20</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vesterbækvej 31</t>
+          <t xml:space="preserve">Bredgade 55</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3576,30 +3576,30 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">7427707</t>
+          <t xml:space="preserve">5107640</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J48">
-        <v>2030</v>
+        <v>718</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311832916</t>
+          <t xml:space="preserve">311844281</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweco Danmark A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-20</t>
+          <t xml:space="preserve">2035-07-11</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3641,7 +3641,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bredgade 55</t>
+          <t xml:space="preserve">Lerpøtvej 50A</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3651,7 +3651,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">5107640</t>
+          <t xml:space="preserve">5755831</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3660,11 +3660,11 @@
         </is>
       </c>
       <c r="J49">
-        <v>718</v>
+        <v>521</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311844281</t>
+          <t xml:space="preserve">311844284</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lerpøtvej 50A</t>
+          <t xml:space="preserve">Lerpøtvej 50B</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3731,11 +3731,11 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J50">
-        <v>521</v>
+        <v>674</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lerpøtvej 50B</t>
+          <t xml:space="preserve">Lerpøtvej 50C</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3806,11 +3806,11 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J51">
-        <v>674</v>
+        <v>709</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -3866,30 +3866,30 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lerpøtvej 50C</t>
+          <t xml:space="preserve">Storegade 59</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6855</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">5755831</t>
+          <t xml:space="preserve">7968232</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J52">
-        <v>709</v>
+        <v>612</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311844284</t>
+          <t xml:space="preserve">311844285</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3956,11 +3956,11 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J53">
-        <v>612</v>
+        <v>1830</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -4031,11 +4031,11 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J54">
-        <v>1830</v>
+        <v>233</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -4106,11 +4106,11 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J55">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -4181,11 +4181,11 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J56">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -4241,40 +4241,40 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storegade 59</t>
+          <t xml:space="preserve">Sønderalle 7</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">6855</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">7968232</t>
+          <t xml:space="preserve">8443476</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J57">
-        <v>210</v>
+        <v>449</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311844285</t>
+          <t xml:space="preserve">311863487</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-11</t>
+          <t xml:space="preserve">2035-10-22</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønderalle 7</t>
+          <t xml:space="preserve">Krovej 11B</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">8443476</t>
+          <t xml:space="preserve">8296451</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4335,21 +4335,21 @@
         </is>
       </c>
       <c r="J58">
-        <v>449</v>
+        <v>635</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311863487</t>
+          <t xml:space="preserve">311869486</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweco Danmark A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-22</t>
+          <t xml:space="preserve">2035-11-20</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krovej 11B</t>
+          <t xml:space="preserve">Troesmosevej 2</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">8296451</t>
+          <t xml:space="preserve">9998735</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4410,11 +4410,11 @@
         </is>
       </c>
       <c r="J59">
-        <v>635</v>
+        <v>1403</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311869486</t>
+          <t xml:space="preserve">311869806</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-20</t>
+          <t xml:space="preserve">2035-11-24</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4481,11 +4481,11 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J60">
-        <v>1403</v>
+        <v>3244</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -4556,11 +4556,11 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J61">
-        <v>3244</v>
+        <v>634</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -4631,15 +4631,15 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J62">
-        <v>634</v>
+        <v>973</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311869806</t>
+          <t xml:space="preserve">311869804</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4691,30 +4691,30 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Troesmosevej 2</t>
+          <t xml:space="preserve">Byagervej 10</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6830</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">9998735</t>
+          <t xml:space="preserve">5099694</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J63">
-        <v>973</v>
+        <v>126</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311869804</t>
+          <t xml:space="preserve">311876600</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-24</t>
+          <t xml:space="preserve">2036-01-14</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byagervej 10</t>
+          <t xml:space="preserve">Byagervej 14</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J64">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byagervej 14</t>
+          <t xml:space="preserve">Byagervej 18</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J65">
@@ -4916,30 +4916,30 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byagervej 18</t>
+          <t xml:space="preserve">Fredensvej 1</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">6830</t>
+          <t xml:space="preserve">6840</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">5099694</t>
+          <t xml:space="preserve">5088173</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J66">
-        <v>126</v>
+        <v>63</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311876600</t>
+          <t xml:space="preserve">311876611</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fredensvej 1</t>
+          <t xml:space="preserve">Fredensvej 11</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J67">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fredensvej 11</t>
+          <t xml:space="preserve">Fredensvej 12</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5081,11 +5081,11 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J68">
-        <v>63</v>
+        <v>130</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fredensvej 12</t>
+          <t xml:space="preserve">Fredensvej 13</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5156,11 +5156,11 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J69">
-        <v>130</v>
+        <v>63</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fredensvej 13</t>
+          <t xml:space="preserve">Fredensvej 16</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5231,11 +5231,11 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J70">
-        <v>63</v>
+        <v>130</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fredensvej 16</t>
+          <t xml:space="preserve">Fredensvej 3</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5306,11 +5306,11 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J71">
-        <v>130</v>
+        <v>63</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fredensvej 3</t>
+          <t xml:space="preserve">Fredensvej 4</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J72">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fredensvej 4</t>
+          <t xml:space="preserve">Fredensvej 5</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J73">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fredensvej 5</t>
+          <t xml:space="preserve">Fredensvej 6</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J74">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fredensvej 6</t>
+          <t xml:space="preserve">Fredensvej 7</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J75">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fredensvej 7</t>
+          <t xml:space="preserve">Fredensvej 9</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J76">
@@ -5741,30 +5741,30 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fredensvej 9</t>
+          <t xml:space="preserve">Nørregade 7A</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">6840</t>
+          <t xml:space="preserve">6870</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">5088173</t>
+          <t xml:space="preserve">5081870</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J77">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311876611</t>
+          <t xml:space="preserve">311876602</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 7A</t>
+          <t xml:space="preserve">Nørregade 7B</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J78">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 7B</t>
+          <t xml:space="preserve">Nørregade 7D</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J79">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 7D</t>
+          <t xml:space="preserve">Nørregade 7E</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J80">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 7E</t>
+          <t xml:space="preserve">Nørregade 7F</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -6056,7 +6056,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J81">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 7F</t>
+          <t xml:space="preserve">Nørregade 7G</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J82">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 7G</t>
+          <t xml:space="preserve">Nørregade 7H</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J83">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 7H</t>
+          <t xml:space="preserve">Nørregade 7K</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J84">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 7K</t>
+          <t xml:space="preserve">Nørregade 7L</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J85">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 7L</t>
+          <t xml:space="preserve">Nørregade 7M</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J86">
@@ -6491,30 +6491,30 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 7M</t>
+          <t xml:space="preserve">Blüchers Alle 9</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">6870</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">5081870</t>
+          <t xml:space="preserve">5135329</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J87">
-        <v>60</v>
+        <v>494</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311876602</t>
+          <t xml:space="preserve">311876778</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-14</t>
+          <t xml:space="preserve">2036-01-15</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6566,30 +6566,30 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blüchers Alle 9</t>
+          <t xml:space="preserve">Fåborgvej 88A</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6753</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">5135329</t>
+          <t xml:space="preserve">5112164</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J88">
-        <v>494</v>
+        <v>237</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311876778</t>
+          <t xml:space="preserve">311876777</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fåborgvej 88A</t>
+          <t xml:space="preserve">Fåborgvej 90</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -6656,15 +6656,15 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J89">
-        <v>237</v>
+        <v>408</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311876777</t>
+          <t xml:space="preserve">311876768</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6716,17 +6716,17 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fåborgvej 90</t>
+          <t xml:space="preserve">Skolegade 15</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">6753</t>
+          <t xml:space="preserve">6870</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">5112164</t>
+          <t xml:space="preserve">5081153</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -6735,11 +6735,11 @@
         </is>
       </c>
       <c r="J90">
-        <v>408</v>
+        <v>250</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311876768</t>
+          <t xml:space="preserve">311876774</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 15</t>
+          <t xml:space="preserve">Skolegade 24</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -6801,20 +6801,20 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">5081153</t>
+          <t xml:space="preserve">5081116</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J91">
-        <v>250</v>
+        <v>351</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311876774</t>
+          <t xml:space="preserve">311876773</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 24</t>
+          <t xml:space="preserve">Skolegade 25</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -6876,20 +6876,20 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">5081116</t>
+          <t xml:space="preserve">5081191</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J92">
-        <v>351</v>
+        <v>2264</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311876773</t>
+          <t xml:space="preserve">311876775</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6941,17 +6941,17 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 25</t>
+          <t xml:space="preserve">Sønderskovvej 107</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">6870</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">5081191</t>
+          <t xml:space="preserve">5135329</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6960,11 +6960,11 @@
         </is>
       </c>
       <c r="J93">
-        <v>2264</v>
+        <v>4847</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311876775</t>
+          <t xml:space="preserve">311876769</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -7016,17 +7016,17 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønderskovvej 107</t>
+          <t xml:space="preserve">Debelvej 23</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6753</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">5135329</t>
+          <t xml:space="preserve">5112771</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -7035,11 +7035,11 @@
         </is>
       </c>
       <c r="J94">
-        <v>4847</v>
+        <v>5820</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311876769</t>
+          <t xml:space="preserve">311878341</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-15</t>
+          <t xml:space="preserve">2036-01-23</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7106,11 +7106,11 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J95">
-        <v>5820</v>
+        <v>1100</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
@@ -7166,7 +7166,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Debelvej 23</t>
+          <t xml:space="preserve">Debelvej 25</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">5112771</t>
+          <t xml:space="preserve">100043834</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -7185,11 +7185,11 @@
         </is>
       </c>
       <c r="J96">
-        <v>1100</v>
+        <v>620</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878341</t>
+          <t xml:space="preserve">311878336</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -7241,30 +7241,30 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Debelvej 25</t>
+          <t xml:space="preserve">Højgårdsparken 69</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">6753</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">100043834</t>
+          <t xml:space="preserve">100064656</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J97">
-        <v>620</v>
+        <v>108</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878336</t>
+          <t xml:space="preserve">311878339</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -7316,17 +7316,17 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højgårdsparken 69</t>
+          <t xml:space="preserve">Stationsvej 2A</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6823</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">100064656</t>
+          <t xml:space="preserve">5075657</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -7335,11 +7335,11 @@
         </is>
       </c>
       <c r="J98">
-        <v>108</v>
+        <v>60</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878339</t>
+          <t xml:space="preserve">311878457</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -7349,7 +7349,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-23</t>
+          <t xml:space="preserve">2036-01-24</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stationsvej 2A</t>
+          <t xml:space="preserve">Stationsvej 2B</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J99">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stationsvej 2B</t>
+          <t xml:space="preserve">Stationsvej 2C</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -7481,7 +7481,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J100">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stationsvej 2C</t>
+          <t xml:space="preserve">Stationsvej 2D</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -7551,12 +7551,12 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">5075657</t>
+          <t xml:space="preserve">5075762</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J101">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878457</t>
+          <t xml:space="preserve">311878458</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stationsvej 2D</t>
+          <t xml:space="preserve">Stationsvej 2E</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J102">
@@ -7691,30 +7691,30 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stationsvej 2E</t>
+          <t xml:space="preserve">Søndergade 76</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">6823</t>
+          <t xml:space="preserve">6870</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">5075762</t>
+          <t xml:space="preserve">5082503</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J103">
-        <v>60</v>
+        <v>264</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878458</t>
+          <t xml:space="preserve">311878455</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -7781,11 +7781,11 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J104">
-        <v>264</v>
+        <v>198</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J105">
@@ -7916,30 +7916,30 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergade 76</t>
+          <t xml:space="preserve">Falkevej 4A</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">6870</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">5082503</t>
+          <t xml:space="preserve">317690, 317691</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J106">
-        <v>198</v>
+        <v>1070</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878455</t>
+          <t xml:space="preserve">311878488</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-24</t>
+          <t xml:space="preserve">2036-01-25</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Falkevej 4A</t>
+          <t xml:space="preserve">Højvangen 4</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">317690, 317691</t>
+          <t xml:space="preserve">5078282</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -8010,11 +8010,11 @@
         </is>
       </c>
       <c r="J107">
-        <v>1070</v>
+        <v>457</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878488</t>
+          <t xml:space="preserve">311878485</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højvangen 4</t>
+          <t xml:space="preserve">Mælkevejen 1</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -8076,20 +8076,20 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">5078282</t>
+          <t xml:space="preserve">5078139</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J108">
-        <v>457</v>
+        <v>209</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878485</t>
+          <t xml:space="preserve">311878489</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -8156,15 +8156,15 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J109">
-        <v>209</v>
+        <v>1440</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878489</t>
+          <t xml:space="preserve">311878543</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-25</t>
+          <t xml:space="preserve">2036-01-26</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8231,11 +8231,11 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J110">
-        <v>1440</v>
+        <v>554</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
@@ -8291,30 +8291,30 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mælkevejen 1</t>
+          <t xml:space="preserve">Møllevej 1</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6818</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">5078139</t>
+          <t xml:space="preserve">5113229</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J111">
-        <v>554</v>
+        <v>380</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878543</t>
+          <t xml:space="preserve">311878765</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-26</t>
+          <t xml:space="preserve">2036-01-27</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8366,17 +8366,17 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllevej 1</t>
+          <t xml:space="preserve">Egekrattet 10</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">6818</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">5113229</t>
+          <t xml:space="preserve">8165975</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -8385,11 +8385,11 @@
         </is>
       </c>
       <c r="J112">
-        <v>380</v>
+        <v>451</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878765</t>
+          <t xml:space="preserve">311881488</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -8399,7 +8399,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-27</t>
+          <t xml:space="preserve">2036-02-11</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egekrattet 10</t>
+          <t xml:space="preserve">Egekrattet 8</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -8451,7 +8451,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">8165975</t>
+          <t xml:space="preserve">8165976</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -8460,11 +8460,11 @@
         </is>
       </c>
       <c r="J113">
-        <v>451</v>
+        <v>370</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311881488</t>
+          <t xml:space="preserve">311881489</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egekrattet 8</t>
+          <t xml:space="preserve">Kærhøgevej 2</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -8526,7 +8526,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">8165976</t>
+          <t xml:space="preserve">1809437</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -8535,11 +8535,11 @@
         </is>
       </c>
       <c r="J114">
-        <v>370</v>
+        <v>497</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311881489</t>
+          <t xml:space="preserve">311881487</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -8591,17 +8591,17 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kærhøgevej 2</t>
+          <t xml:space="preserve">Skolegade 22</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6870</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">1809437</t>
+          <t xml:space="preserve">5081117</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -8610,11 +8610,11 @@
         </is>
       </c>
       <c r="J115">
-        <v>497</v>
+        <v>1693</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311881487</t>
+          <t xml:space="preserve">311881490</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -8666,17 +8666,17 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 22</t>
+          <t xml:space="preserve">Stationsvej 19</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">6870</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">5081117</t>
+          <t xml:space="preserve">5079228</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -8685,11 +8685,11 @@
         </is>
       </c>
       <c r="J116">
-        <v>1693</v>
+        <v>528</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311881490</t>
+          <t xml:space="preserve">311881512</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stationsvej 19</t>
+          <t xml:space="preserve">Thorstrupvej 14</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -8751,7 +8751,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">5079228</t>
+          <t xml:space="preserve">5078819</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -8760,11 +8760,11 @@
         </is>
       </c>
       <c r="J117">
-        <v>528</v>
+        <v>381</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311881512</t>
+          <t xml:space="preserve">311881515</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thorstrupvej 14</t>
+          <t xml:space="preserve">Thorstrupvej 16</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -8831,15 +8831,15 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J118">
-        <v>381</v>
+        <v>296</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311881515</t>
+          <t xml:space="preserve">311881519</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -8891,7 +8891,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thorstrupvej 16</t>
+          <t xml:space="preserve">Thorstrupvej 18</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -8901,20 +8901,20 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">5078819</t>
+          <t xml:space="preserve">5078814</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J119">
-        <v>296</v>
+        <v>3019</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311881519</t>
+          <t xml:space="preserve">311881536</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -8966,17 +8966,17 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thorstrupvej 18</t>
+          <t xml:space="preserve">Grødevej 7</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6823</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">5078814</t>
+          <t xml:space="preserve">5076159</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -8985,11 +8985,11 @@
         </is>
       </c>
       <c r="J120">
-        <v>3019</v>
+        <v>423</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311881536</t>
+          <t xml:space="preserve">311881912</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-11</t>
+          <t xml:space="preserve">2036-02-13</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -9041,30 +9041,30 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grødevej 7</t>
+          <t xml:space="preserve">Stilbjergvej 30</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">6823</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">5076159</t>
+          <t xml:space="preserve">5759719</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J121">
-        <v>423</v>
+        <v>151</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311881912</t>
+          <t xml:space="preserve">311882129</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-13</t>
+          <t xml:space="preserve">2036-02-16</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -9116,7 +9116,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stilbjergvej 30</t>
+          <t xml:space="preserve">Bredgade 39</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -9126,20 +9126,20 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">5759719</t>
+          <t xml:space="preserve">5107083</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J122">
-        <v>151</v>
+        <v>3381</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311882129</t>
+          <t xml:space="preserve">311883233</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-16</t>
+          <t xml:space="preserve">2036-02-20</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9191,17 +9191,17 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bredgade 39</t>
+          <t xml:space="preserve">Gartnerpassagen 6</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6870</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">5107083</t>
+          <t xml:space="preserve">5082163</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -9210,11 +9210,11 @@
         </is>
       </c>
       <c r="J123">
-        <v>3381</v>
+        <v>4305</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311883233</t>
+          <t xml:space="preserve">311883263</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -9266,17 +9266,17 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gartnerpassagen 6</t>
+          <t xml:space="preserve">Jægumsvej 44</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">6870</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">5082163</t>
+          <t xml:space="preserve">5758115</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -9285,11 +9285,11 @@
         </is>
       </c>
       <c r="J124">
-        <v>4305</v>
+        <v>643</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311883263</t>
+          <t xml:space="preserve">311883267</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -9341,17 +9341,17 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jægumsvej 44</t>
+          <t xml:space="preserve">Kildegårdvej 14</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6852</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">5758115</t>
+          <t xml:space="preserve">5089317</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -9360,11 +9360,11 @@
         </is>
       </c>
       <c r="J125">
-        <v>643</v>
+        <v>1744</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311883267</t>
+          <t xml:space="preserve">311883204</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -9416,17 +9416,17 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildegårdvej 14</t>
+          <t xml:space="preserve">Kløvbakken 70</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">6852</t>
+          <t xml:space="preserve">6855</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">5089317</t>
+          <t xml:space="preserve">8245265</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -9435,11 +9435,11 @@
         </is>
       </c>
       <c r="J126">
-        <v>1744</v>
+        <v>452</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311883204</t>
+          <t xml:space="preserve">311883265</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -9506,11 +9506,11 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J127">
-        <v>452</v>
+        <v>68</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
@@ -9566,30 +9566,30 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kløvbakken 70</t>
+          <t xml:space="preserve">Krogen 1</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">6855</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">8245265</t>
+          <t xml:space="preserve">5755579</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J128">
-        <v>68</v>
+        <v>366</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311883265</t>
+          <t xml:space="preserve">311883234</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -9641,7 +9641,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krogen 1</t>
+          <t xml:space="preserve">Pramstedvej 10C</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -9651,7 +9651,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">5755579</t>
+          <t xml:space="preserve">5755568</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -9660,11 +9660,11 @@
         </is>
       </c>
       <c r="J129">
-        <v>366</v>
+        <v>8223</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311883234</t>
+          <t xml:space="preserve">311883211</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pramstedvej 10C</t>
+          <t xml:space="preserve">Pramstedvej 12B</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -9726,20 +9726,20 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">5755568</t>
+          <t xml:space="preserve">5759376</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J130">
-        <v>8223</v>
+        <v>504</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311883211</t>
+          <t xml:space="preserve">311883210</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pramstedvej 12B</t>
+          <t xml:space="preserve">Pramstedvej 12C</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -9806,15 +9806,15 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J131">
-        <v>504</v>
+        <v>171</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311883210</t>
+          <t xml:space="preserve">311883208</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pramstedvej 12C</t>
+          <t xml:space="preserve">Pramstedvej 12D</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J132">
@@ -9889,7 +9889,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311883208</t>
+          <t xml:space="preserve">311883209</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pramstedvej 12D</t>
+          <t xml:space="preserve">Storegade 57</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -9951,20 +9951,20 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">5759376</t>
+          <t xml:space="preserve">5754327</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J133">
-        <v>171</v>
+        <v>1377</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311883209</t>
+          <t xml:space="preserve">311883205</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -10016,17 +10016,17 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storegade 57</t>
+          <t xml:space="preserve">Torvet 9</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6823</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">5754327</t>
+          <t xml:space="preserve">7925073</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -10035,11 +10035,11 @@
         </is>
       </c>
       <c r="J134">
-        <v>1377</v>
+        <v>234</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311883205</t>
+          <t xml:space="preserve">311883262</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -10091,17 +10091,17 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torvet 9</t>
+          <t xml:space="preserve">Vestergade 20</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">6823</t>
+          <t xml:space="preserve">6840</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">7925073</t>
+          <t xml:space="preserve">5088167</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -10110,11 +10110,11 @@
         </is>
       </c>
       <c r="J135">
-        <v>234</v>
+        <v>3489</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311883262</t>
+          <t xml:space="preserve">311883264</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -10166,17 +10166,17 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 20</t>
+          <t xml:space="preserve">Østervang 1</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">6840</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">5088167</t>
+          <t xml:space="preserve">5757498</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -10185,11 +10185,11 @@
         </is>
       </c>
       <c r="J136">
-        <v>3489</v>
+        <v>502</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311883264</t>
+          <t xml:space="preserve">311883232</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østervang 1</t>
+          <t xml:space="preserve">Bredgade 35</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -10251,20 +10251,20 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">5757498</t>
+          <t xml:space="preserve">5107083</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J137">
-        <v>502</v>
+        <v>123</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311883232</t>
+          <t xml:space="preserve">311883506</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-20</t>
+          <t xml:space="preserve">2036-02-23</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10316,7 +10316,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bredgade 35</t>
+          <t xml:space="preserve">Bredgade 37</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -10331,11 +10331,11 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J138">
-        <v>123</v>
+        <v>244</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bredgade 37</t>
+          <t xml:space="preserve">Dalgasvej 35</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -10401,20 +10401,20 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">5107083</t>
+          <t xml:space="preserve">5754804</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J139">
-        <v>244</v>
+        <v>413</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311883506</t>
+          <t xml:space="preserve">311888577</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -10424,7 +10424,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-23</t>
+          <t xml:space="preserve">2036-03-19</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10481,11 +10481,11 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J140">
-        <v>413</v>
+        <v>374</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dalgasvej 35</t>
+          <t xml:space="preserve">Isbjerg Møllevej 69A</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -10551,20 +10551,20 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">5754804</t>
+          <t xml:space="preserve">10002269</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J141">
-        <v>374</v>
+        <v>285</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888577</t>
+          <t xml:space="preserve">311888784</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -10616,7 +10616,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isbjerg Møllevej 69A</t>
+          <t xml:space="preserve">Isbjerg Møllevej 69B</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -10631,15 +10631,15 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J142">
-        <v>285</v>
+        <v>148</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888784</t>
+          <t xml:space="preserve">311888782</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -10691,17 +10691,17 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isbjerg Møllevej 69B</t>
+          <t xml:space="preserve">Rosenvænget 31</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6870</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">10002269</t>
+          <t xml:space="preserve">7767753</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -10710,11 +10710,11 @@
         </is>
       </c>
       <c r="J143">
-        <v>148</v>
+        <v>335</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888782</t>
+          <t xml:space="preserve">311888779</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -10781,11 +10781,11 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J144">
-        <v>335</v>
+        <v>490</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
@@ -10856,11 +10856,11 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J145">
-        <v>490</v>
+        <v>157</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
@@ -10931,11 +10931,11 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J146">
-        <v>157</v>
+        <v>105</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
@@ -11006,15 +11006,15 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J147">
-        <v>105</v>
+        <v>196</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888779</t>
+          <t xml:space="preserve">311888781</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -11066,30 +11066,30 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenvænget 31</t>
+          <t xml:space="preserve">Skolegade 25</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">6870</t>
+          <t xml:space="preserve">6818</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">7767753</t>
+          <t xml:space="preserve">5106531</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J148">
-        <v>196</v>
+        <v>419</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888781</t>
+          <t xml:space="preserve">311888764</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -11141,30 +11141,30 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 25</t>
+          <t xml:space="preserve">Skolegade 27F</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">6818</t>
+          <t xml:space="preserve">6830</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">5106531</t>
+          <t xml:space="preserve">100083815</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J149">
-        <v>419</v>
+        <v>985</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888764</t>
+          <t xml:space="preserve">311888580</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -11216,17 +11216,17 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 27F</t>
+          <t xml:space="preserve">Svanehøjvej 27</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">6830</t>
+          <t xml:space="preserve">6870</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">100083815</t>
+          <t xml:space="preserve">9212270</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -11235,11 +11235,11 @@
         </is>
       </c>
       <c r="J150">
-        <v>985</v>
+        <v>2216</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888580</t>
+          <t xml:space="preserve">311888785</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -11291,30 +11291,30 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svanehøjvej 27</t>
+          <t xml:space="preserve">Toften 2H</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">6870</t>
+          <t xml:space="preserve">6818</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">9212270</t>
+          <t xml:space="preserve">5106531</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J151">
-        <v>2216</v>
+        <v>512</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888785</t>
+          <t xml:space="preserve">311888770</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -11366,30 +11366,30 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toften 2H</t>
+          <t xml:space="preserve">Vadgårdsvej 17</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">6818</t>
+          <t xml:space="preserve">6830</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">5106531</t>
+          <t xml:space="preserve">5099212</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J152">
-        <v>512</v>
+        <v>525</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888770</t>
+          <t xml:space="preserve">311888780</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -11441,17 +11441,17 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vadgårdsvej 17</t>
+          <t xml:space="preserve">Vardevej 1A</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">6830</t>
+          <t xml:space="preserve">6818</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">5099212</t>
+          <t xml:space="preserve">5106531</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -11460,11 +11460,11 @@
         </is>
       </c>
       <c r="J153">
-        <v>525</v>
+        <v>2544</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888780</t>
+          <t xml:space="preserve">311888776</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vardevej 1A</t>
+          <t xml:space="preserve">Vardevej 1B</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -11531,15 +11531,15 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J154">
-        <v>2544</v>
+        <v>428</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888776</t>
+          <t xml:space="preserve">311888760</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -11591,30 +11591,30 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vardevej 1B</t>
+          <t xml:space="preserve">Vestervold 11A</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">6818</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">5106531</t>
+          <t xml:space="preserve">5756377</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J155">
-        <v>428</v>
+        <v>1527</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888760</t>
+          <t xml:space="preserve">311888579</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -11666,7 +11666,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestervold 11A</t>
+          <t xml:space="preserve">Vestervold 11C</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -11676,7 +11676,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">5756377</t>
+          <t xml:space="preserve">5756447</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -11685,11 +11685,11 @@
         </is>
       </c>
       <c r="J156">
-        <v>1527</v>
+        <v>384</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888579</t>
+          <t xml:space="preserve">311888578</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -11741,7 +11741,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestervold 11C</t>
+          <t xml:space="preserve">Vestervold 11D</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -11751,20 +11751,20 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">5756447</t>
+          <t xml:space="preserve">5756377</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J157">
-        <v>384</v>
+        <v>154</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888578</t>
+          <t xml:space="preserve">311888579</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestervold 11D</t>
+          <t xml:space="preserve">Abildvej 25</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -11826,20 +11826,20 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">5756377</t>
+          <t xml:space="preserve">1511385</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J158">
-        <v>154</v>
+        <v>3442</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888579</t>
+          <t xml:space="preserve">311888935</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -11849,7 +11849,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-19</t>
+          <t xml:space="preserve">2036-03-20</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11906,11 +11906,11 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J159">
-        <v>3442</v>
+        <v>969</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
@@ -11981,11 +11981,11 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J160">
-        <v>969</v>
+        <v>1067</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
@@ -12056,11 +12056,11 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J161">
-        <v>1067</v>
+        <v>1052</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
@@ -12116,7 +12116,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Abildvej 25</t>
+          <t xml:space="preserve">Abildvej 35</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -12131,15 +12131,15 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J162">
-        <v>1052</v>
+        <v>1970</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888935</t>
+          <t xml:space="preserve">311888912</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -12191,30 +12191,30 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Abildvej 35</t>
+          <t xml:space="preserve">Kirkegade 3</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6840</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">1511385</t>
+          <t xml:space="preserve">8367028</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J163">
-        <v>1970</v>
+        <v>147</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888912</t>
+          <t xml:space="preserve">311888953</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -12266,17 +12266,17 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkegade 3</t>
+          <t xml:space="preserve">Lindealle 8</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">6840</t>
+          <t xml:space="preserve">6870</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">8367028</t>
+          <t xml:space="preserve">5081802</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -12285,11 +12285,11 @@
         </is>
       </c>
       <c r="J164">
-        <v>147</v>
+        <v>778</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888953</t>
+          <t xml:space="preserve">311888957</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -12341,7 +12341,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindealle 8</t>
+          <t xml:space="preserve">Skolegade 11</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -12351,20 +12351,20 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">5081802</t>
+          <t xml:space="preserve">5081139</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J165">
-        <v>778</v>
+        <v>1624</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888957</t>
+          <t xml:space="preserve">311888955</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -12431,11 +12431,11 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J166">
-        <v>1624</v>
+        <v>2910</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
@@ -12506,11 +12506,11 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J167">
-        <v>2910</v>
+        <v>740</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
@@ -12581,11 +12581,11 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J168">
-        <v>740</v>
+        <v>460</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
@@ -12656,11 +12656,11 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J169">
-        <v>460</v>
+        <v>241</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
@@ -12716,30 +12716,30 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 11</t>
+          <t xml:space="preserve">Bytoften 2</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">6870</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">5081139</t>
+          <t xml:space="preserve">5756643</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J170">
-        <v>241</v>
+        <v>6003</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888955</t>
+          <t xml:space="preserve">311892635</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-20</t>
+          <t xml:space="preserve">2036-04-08</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bytoften 2</t>
+          <t xml:space="preserve">Flyvepladsvej 2B</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -12801,20 +12801,20 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">5756643</t>
+          <t xml:space="preserve">5107795</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J171">
-        <v>6003</v>
+        <v>265</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892635</t>
+          <t xml:space="preserve">311892714</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -12866,7 +12866,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flyvepladsvej 2B</t>
+          <t xml:space="preserve">Kirkegade 1B</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -12876,20 +12876,20 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">5107795</t>
+          <t xml:space="preserve">5107190</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J172">
-        <v>265</v>
+        <v>1435</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892714</t>
+          <t xml:space="preserve">311892637</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -12941,30 +12941,30 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkegade 1B</t>
+          <t xml:space="preserve">Kirkegade 60</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6840</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">5107190</t>
+          <t xml:space="preserve">9722879</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J173">
-        <v>1435</v>
+        <v>783</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892637</t>
+          <t xml:space="preserve">311892648</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -13016,30 +13016,30 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkegade 60</t>
+          <t xml:space="preserve">Krogen 3</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">6840</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">9722879</t>
+          <t xml:space="preserve">100019865</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J174">
-        <v>783</v>
+        <v>799</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892648</t>
+          <t xml:space="preserve">311892885</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -13091,7 +13091,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krogen 3</t>
+          <t xml:space="preserve">Krogen 5</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -13106,15 +13106,15 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J175">
-        <v>799</v>
+        <v>827</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892885</t>
+          <t xml:space="preserve">311892716</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -13166,7 +13166,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krogen 5</t>
+          <t xml:space="preserve">Krogen 7</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -13181,15 +13181,15 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J176">
-        <v>827</v>
+        <v>114</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892716</t>
+          <t xml:space="preserve">311892886</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -13241,7 +13241,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krogen 7</t>
+          <t xml:space="preserve">Pramstedvej 6</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -13251,20 +13251,20 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">100019865</t>
+          <t xml:space="preserve">5755576</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J177">
-        <v>114</v>
+        <v>1289</v>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892886</t>
+          <t xml:space="preserve">311892803</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -13316,30 +13316,30 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pramstedvej 6</t>
+          <t xml:space="preserve">Smedebakken 14</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">7200</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">5755576</t>
+          <t xml:space="preserve">5130812</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J178">
-        <v>1289</v>
+        <v>672</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892803</t>
+          <t xml:space="preserve">311892655</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -13391,7 +13391,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smedebakken 14</t>
+          <t xml:space="preserve">Smedebakken 16</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -13406,15 +13406,15 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J179">
-        <v>672</v>
+        <v>1285</v>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892655</t>
+          <t xml:space="preserve">311892656</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -13481,11 +13481,11 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J180">
-        <v>1285</v>
+        <v>815</v>
       </c>
       <c r="K180" t="inlineStr">
         <is>
@@ -13556,15 +13556,15 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J181">
-        <v>815</v>
+        <v>402</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892656</t>
+          <t xml:space="preserve">311892652</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -13616,30 +13616,30 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smedebakken 16</t>
+          <t xml:space="preserve">Sønder Allé 18A</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">7200</t>
+          <t xml:space="preserve">6830</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">5130812</t>
+          <t xml:space="preserve">5098976</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J182">
-        <v>402</v>
+        <v>3082</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892652</t>
+          <t xml:space="preserve">311892807</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -13706,11 +13706,11 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J183">
-        <v>3082</v>
+        <v>1082</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
@@ -13781,7 +13781,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J184">
@@ -13856,11 +13856,11 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J185">
-        <v>1082</v>
+        <v>343</v>
       </c>
       <c r="K185" t="inlineStr">
         <is>
@@ -13916,7 +13916,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønder Allé 18A</t>
+          <t xml:space="preserve">Sønder Allé 18B</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -13926,20 +13926,20 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">5098976</t>
+          <t xml:space="preserve">5098950</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J186">
-        <v>343</v>
+        <v>664</v>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892807</t>
+          <t xml:space="preserve">311892805</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -14006,11 +14006,11 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J187">
-        <v>664</v>
+        <v>1460</v>
       </c>
       <c r="K187" t="inlineStr">
         <is>
@@ -14066,30 +14066,30 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønder Allé 18B</t>
+          <t xml:space="preserve">Vestergade 27</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">6830</t>
+          <t xml:space="preserve">6840</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">5098950</t>
+          <t xml:space="preserve">5087533</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J188">
-        <v>1460</v>
+        <v>293</v>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892805</t>
+          <t xml:space="preserve">311892646</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -14141,7 +14141,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 27</t>
+          <t xml:space="preserve">Vestergade 31</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -14156,15 +14156,15 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J189">
-        <v>293</v>
+        <v>450</v>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892646</t>
+          <t xml:space="preserve">311892645</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -14216,30 +14216,30 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 31</t>
+          <t xml:space="preserve">Viaduktvej 25B</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">6840</t>
+          <t xml:space="preserve">6870</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">5087533</t>
+          <t xml:space="preserve">5083002</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J190">
-        <v>450</v>
+        <v>505</v>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892645</t>
+          <t xml:space="preserve">311892650</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -14291,17 +14291,17 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Viaduktvej 25B</t>
+          <t xml:space="preserve">Østervang 3A</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">6870</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">5083002</t>
+          <t xml:space="preserve">8257259</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -14310,11 +14310,11 @@
         </is>
       </c>
       <c r="J191">
-        <v>505</v>
+        <v>1222</v>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892650</t>
+          <t xml:space="preserve">311892719</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -14366,7 +14366,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østervang 3A</t>
+          <t xml:space="preserve">Lundvej 135A</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -14376,7 +14376,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">8257259</t>
+          <t xml:space="preserve">1511389</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -14385,11 +14385,11 @@
         </is>
       </c>
       <c r="J192">
-        <v>1222</v>
+        <v>3433</v>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892719</t>
+          <t xml:space="preserve">311895818</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -14399,7 +14399,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-08</t>
+          <t xml:space="preserve">2036-04-22</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -14456,11 +14456,11 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J193">
-        <v>3433</v>
+        <v>1008</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
@@ -14531,11 +14531,11 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J194">
-        <v>1008</v>
+        <v>827</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
@@ -14591,7 +14591,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundvej 135A</t>
+          <t xml:space="preserve">Lundvej 135B</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -14606,15 +14606,15 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J195">
-        <v>827</v>
+        <v>365</v>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311895818</t>
+          <t xml:space="preserve">311895828</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -14681,15 +14681,15 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J196">
-        <v>365</v>
+        <v>859</v>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311895828</t>
+          <t xml:space="preserve">311895826</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -14741,7 +14741,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundvej 135B</t>
+          <t xml:space="preserve">Abildvej 25</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -14751,20 +14751,20 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">1511389</t>
+          <t xml:space="preserve">8443476</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J197">
-        <v>859</v>
+        <v>1632</v>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311895826</t>
+          <t xml:space="preserve">311896763</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -14774,7 +14774,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-22</t>
+          <t xml:space="preserve">2036-04-24</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14831,11 +14831,11 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J198">
-        <v>1632</v>
+        <v>2198</v>
       </c>
       <c r="K198" t="inlineStr">
         <is>
@@ -14891,30 +14891,30 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Abildvej 25</t>
+          <t xml:space="preserve">Byagervej 19</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6830</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve">8443476</t>
+          <t xml:space="preserve">5099692</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J199">
-        <v>2198</v>
+        <v>4785</v>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896763</t>
+          <t xml:space="preserve">311896775</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -14966,17 +14966,17 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byagervej 19</t>
+          <t xml:space="preserve">Carolineparken 1A</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t xml:space="preserve">6830</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">5099692</t>
+          <t xml:space="preserve">5757501</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -14985,11 +14985,11 @@
         </is>
       </c>
       <c r="J200">
-        <v>4785</v>
+        <v>1634</v>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896775</t>
+          <t xml:space="preserve">311896772</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -15041,7 +15041,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carolineparken 1A</t>
+          <t xml:space="preserve">Carolineparken 1G</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -15056,11 +15056,11 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J201">
-        <v>1634</v>
+        <v>567</v>
       </c>
       <c r="K201" t="inlineStr">
         <is>
@@ -15116,30 +15116,30 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carolineparken 1G</t>
+          <t xml:space="preserve">Fåborgvej 151</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6753</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t xml:space="preserve">5757501</t>
+          <t xml:space="preserve">5112648</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J202">
-        <v>567</v>
+        <v>2385</v>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896772</t>
+          <t xml:space="preserve">311896787</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
@@ -15191,30 +15191,30 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fåborgvej 151</t>
+          <t xml:space="preserve">Kirkegade 1C</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t xml:space="preserve">6753</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t xml:space="preserve">5112648</t>
+          <t xml:space="preserve">5107106</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J203">
-        <v>2385</v>
+        <v>390</v>
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896787</t>
+          <t xml:space="preserve">311896773</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
@@ -15266,30 +15266,30 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkegade 1C</t>
+          <t xml:space="preserve">Møllegården 2</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6855</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t xml:space="preserve">5107106</t>
+          <t xml:space="preserve">5106049</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J204">
-        <v>390</v>
+        <v>996</v>
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896773</t>
+          <t xml:space="preserve">311896762</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
@@ -15356,11 +15356,11 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J205">
-        <v>996</v>
+        <v>1078</v>
       </c>
       <c r="K205" t="inlineStr">
         <is>
@@ -15416,30 +15416,30 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllegården 2</t>
+          <t xml:space="preserve">Solhøjvej 1</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t xml:space="preserve">6855</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t xml:space="preserve">5106049</t>
+          <t xml:space="preserve">5134840</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J206">
-        <v>1078</v>
+        <v>760</v>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896762</t>
+          <t xml:space="preserve">311896782</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -15491,17 +15491,17 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solhøjvej 1</t>
+          <t xml:space="preserve">Strandvejen 9B</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6840</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve">5134840</t>
+          <t xml:space="preserve">8939771</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -15510,11 +15510,11 @@
         </is>
       </c>
       <c r="J207">
-        <v>760</v>
+        <v>218</v>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896782</t>
+          <t xml:space="preserve">311896791</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -15566,17 +15566,17 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandvejen 9B</t>
+          <t xml:space="preserve">Stålværksvej 13A</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t xml:space="preserve">6840</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t xml:space="preserve">8939771</t>
+          <t xml:space="preserve">5756440</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -15585,11 +15585,11 @@
         </is>
       </c>
       <c r="J208">
-        <v>218</v>
+        <v>2835</v>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896791</t>
+          <t xml:space="preserve">311896789</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
@@ -15641,7 +15641,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stålværksvej 13A</t>
+          <t xml:space="preserve">Sønderskovvej 33A</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -15651,20 +15651,20 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t xml:space="preserve">5756440</t>
+          <t xml:space="preserve">7277566</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J209">
-        <v>2835</v>
+        <v>431</v>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896789</t>
+          <t xml:space="preserve">311896786</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
@@ -15716,7 +15716,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønderskovvej 33A</t>
+          <t xml:space="preserve">Sønderskovvej 35A</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
@@ -15726,20 +15726,20 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve">7277566</t>
+          <t xml:space="preserve">5134840</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J210">
-        <v>431</v>
+        <v>724</v>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896786</t>
+          <t xml:space="preserve">311896785</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
@@ -15791,30 +15791,30 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønderskovvej 35A</t>
+          <t xml:space="preserve">Torvegade 17</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6840</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t xml:space="preserve">5134840</t>
+          <t xml:space="preserve">8879067</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J211">
-        <v>724</v>
+        <v>537</v>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896785</t>
+          <t xml:space="preserve">311896774</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
@@ -15866,30 +15866,30 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torvegade 17</t>
+          <t xml:space="preserve">Vinkelvej 16A</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t xml:space="preserve">6840</t>
+          <t xml:space="preserve">7200</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t xml:space="preserve">8879067</t>
+          <t xml:space="preserve">5130859</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J212">
-        <v>537</v>
+        <v>977</v>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896774</t>
+          <t xml:space="preserve">311896759</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -15941,7 +15941,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vinkelvej 16A</t>
+          <t xml:space="preserve">Vinkelvej 2</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -15956,11 +15956,11 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J213">
-        <v>977</v>
+        <v>3842</v>
       </c>
       <c r="K213" t="inlineStr">
         <is>
@@ -16016,17 +16016,17 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vinkelvej 2</t>
+          <t xml:space="preserve">Yderikvej 40</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t xml:space="preserve">7200</t>
+          <t xml:space="preserve">6862</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t xml:space="preserve">5130859</t>
+          <t xml:space="preserve">100060726</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -16035,11 +16035,11 @@
         </is>
       </c>
       <c r="J214">
-        <v>3842</v>
+        <v>2426</v>
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896759</t>
+          <t xml:space="preserve">311896788</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -16091,17 +16091,17 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yderikvej 40</t>
+          <t xml:space="preserve">Østergade 17</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t xml:space="preserve">6862</t>
+          <t xml:space="preserve">6823</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t xml:space="preserve">100060726</t>
+          <t xml:space="preserve">5075750</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -16110,11 +16110,11 @@
         </is>
       </c>
       <c r="J215">
-        <v>2426</v>
+        <v>1157</v>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896788</t>
+          <t xml:space="preserve">311896790</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
@@ -16181,11 +16181,11 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J216">
-        <v>1157</v>
+        <v>2462</v>
       </c>
       <c r="K216" t="inlineStr">
         <is>
@@ -16256,11 +16256,11 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J217">
-        <v>2462</v>
+        <v>1302</v>
       </c>
       <c r="K217" t="inlineStr">
         <is>
@@ -16331,11 +16331,11 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J218">
-        <v>1302</v>
+        <v>107</v>
       </c>
       <c r="K218" t="inlineStr">
         <is>
@@ -16406,11 +16406,11 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J219">
-        <v>107</v>
+        <v>450</v>
       </c>
       <c r="K219" t="inlineStr">
         <is>
@@ -16466,30 +16466,30 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 17</t>
+          <t xml:space="preserve">Fyrvej 106</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t xml:space="preserve">6823</t>
+          <t xml:space="preserve">6857</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t xml:space="preserve">5075750</t>
+          <t xml:space="preserve">5101218</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J220">
-        <v>450</v>
+        <v>136</v>
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896790</t>
+          <t xml:space="preserve">311896981</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
@@ -16499,7 +16499,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-24</t>
+          <t xml:space="preserve">2036-04-27</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -16541,17 +16541,17 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fyrvej 106</t>
+          <t xml:space="preserve">Lyngparken 3</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t xml:space="preserve">6857</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t xml:space="preserve">5101218</t>
+          <t xml:space="preserve">5755189</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -16560,11 +16560,11 @@
         </is>
       </c>
       <c r="J221">
-        <v>136</v>
+        <v>1252</v>
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896981</t>
+          <t xml:space="preserve">311896976</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
@@ -16616,30 +16616,30 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngparken 3</t>
+          <t xml:space="preserve">Nybrovej 30</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6851</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t xml:space="preserve">5755189</t>
+          <t xml:space="preserve">736957, 5094333</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J222">
-        <v>1252</v>
+        <v>351</v>
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896976</t>
+          <t xml:space="preserve">311896971</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
@@ -16691,7 +16691,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nybrovej 30</t>
+          <t xml:space="preserve">Nybrovej 32</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -16706,15 +16706,15 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J223">
-        <v>351</v>
+        <v>1533</v>
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896971</t>
+          <t xml:space="preserve">311896972</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
@@ -16766,7 +16766,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nybrovej 32</t>
+          <t xml:space="preserve">Nybrovej 34</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
@@ -16776,20 +16776,20 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t xml:space="preserve">736957, 5094333</t>
+          <t xml:space="preserve">5094366</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J224">
-        <v>1533</v>
+        <v>441</v>
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896972</t>
+          <t xml:space="preserve">311896973</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
@@ -16841,7 +16841,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nybrovej 34</t>
+          <t xml:space="preserve">Nybrovej 36A</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
@@ -16856,15 +16856,15 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J225">
-        <v>441</v>
+        <v>2976</v>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896973</t>
+          <t xml:space="preserve">311896980</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
@@ -16916,17 +16916,17 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nybrovej 36A</t>
+          <t xml:space="preserve">Roustvej 111</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t xml:space="preserve">6851</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t xml:space="preserve">5094366</t>
+          <t xml:space="preserve">5757779</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -16935,11 +16935,11 @@
         </is>
       </c>
       <c r="J226">
-        <v>2976</v>
+        <v>197</v>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896980</t>
+          <t xml:space="preserve">311896968</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
@@ -16991,17 +16991,17 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roustvej 111</t>
+          <t xml:space="preserve">Skolegade 59</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6830</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t xml:space="preserve">5757779</t>
+          <t xml:space="preserve">5096151</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -17010,11 +17010,11 @@
         </is>
       </c>
       <c r="J227">
-        <v>197</v>
+        <v>933</v>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896968</t>
+          <t xml:space="preserve">311896982</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
@@ -17081,11 +17081,11 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J228">
-        <v>933</v>
+        <v>1485</v>
       </c>
       <c r="K228" t="inlineStr">
         <is>
@@ -17141,30 +17141,30 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 59</t>
+          <t xml:space="preserve">Torvet 7</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t xml:space="preserve">6830</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t xml:space="preserve">5096151</t>
+          <t xml:space="preserve">5753906</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J229">
-        <v>1485</v>
+        <v>3584</v>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896982</t>
+          <t xml:space="preserve">311896977</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
@@ -17216,17 +17216,17 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torvet 7</t>
+          <t xml:space="preserve">Vænget 26A</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6818</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t xml:space="preserve">5753906</t>
+          <t xml:space="preserve">5106609</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -17235,16 +17235,16 @@
         </is>
       </c>
       <c r="J230">
-        <v>3584</v>
+        <v>1477</v>
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896978</t>
+          <t xml:space="preserve">311896979</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
@@ -17291,17 +17291,17 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vænget 26A</t>
+          <t xml:space="preserve">Skolevænget 12</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t xml:space="preserve">6818</t>
+          <t xml:space="preserve">6840</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t xml:space="preserve">5106609</t>
+          <t xml:space="preserve">8839667</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -17310,11 +17310,11 @@
         </is>
       </c>
       <c r="J231">
-        <v>1477</v>
+        <v>650</v>
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896979</t>
+          <t xml:space="preserve">311897259</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
@@ -17324,7 +17324,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-27</t>
+          <t xml:space="preserve">2036-04-28</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -17381,15 +17381,15 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J232">
-        <v>650</v>
+        <v>713</v>
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t xml:space="preserve">311897259</t>
+          <t xml:space="preserve">311897257</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
@@ -17456,11 +17456,11 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J233">
-        <v>713</v>
+        <v>240</v>
       </c>
       <c r="K233" t="inlineStr">
         <is>
@@ -17531,15 +17531,15 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J234">
-        <v>240</v>
+        <v>1368</v>
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t xml:space="preserve">311897257</t>
+          <t xml:space="preserve">311897256</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
@@ -17606,7 +17606,7 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J235">
@@ -17681,7 +17681,7 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J236">
@@ -17756,15 +17756,15 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J237">
-        <v>1368</v>
+        <v>217</v>
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t xml:space="preserve">311897256</t>
+          <t xml:space="preserve">311897258</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
@@ -17816,7 +17816,7 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 12</t>
+          <t xml:space="preserve">Skolevænget 12A</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
@@ -17831,15 +17831,15 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J238">
-        <v>217</v>
+        <v>437</v>
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t xml:space="preserve">311897258</t>
+          <t xml:space="preserve">311897264</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
@@ -17891,7 +17891,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 12A</t>
+          <t xml:space="preserve">Skolevænget 19</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
@@ -17901,20 +17901,20 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t xml:space="preserve">8839667</t>
+          <t xml:space="preserve">5087702</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J239">
-        <v>437</v>
+        <v>1155</v>
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t xml:space="preserve">311897264</t>
+          <t xml:space="preserve">311897265</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
@@ -17966,7 +17966,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 19</t>
+          <t xml:space="preserve">Torps Alle 4</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
@@ -17976,7 +17976,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t xml:space="preserve">5087702</t>
+          <t xml:space="preserve">5088166</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -17985,11 +17985,11 @@
         </is>
       </c>
       <c r="J240">
-        <v>1155</v>
+        <v>695</v>
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t xml:space="preserve">311897265</t>
+          <t xml:space="preserve">311897266</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
@@ -18041,7 +18041,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torps Alle 4</t>
+          <t xml:space="preserve">Skolevænget 12</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
@@ -18051,20 +18051,20 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t xml:space="preserve">5088166</t>
+          <t xml:space="preserve">8839667</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J241">
-        <v>695</v>
+        <v>726</v>
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t xml:space="preserve">311897266</t>
+          <t xml:space="preserve">311897625</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-28</t>
+          <t xml:space="preserve">2036-04-29</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -18131,11 +18131,11 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J242">
-        <v>726</v>
+        <v>5084</v>
       </c>
       <c r="K242" t="inlineStr">
         <is>
@@ -18191,30 +18191,30 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 12</t>
+          <t xml:space="preserve">Lerpøtvej 55</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t xml:space="preserve">6840</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t xml:space="preserve">8839667</t>
+          <t xml:space="preserve">5756829</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J243">
-        <v>5084</v>
+        <v>2680</v>
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t xml:space="preserve">311897625</t>
+          <t xml:space="preserve">311918684</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
@@ -18224,7 +18224,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-29</t>
+          <t xml:space="preserve">2036-08-12</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -18281,15 +18281,15 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J244">
-        <v>2680</v>
+        <v>2277</v>
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918684</t>
+          <t xml:space="preserve">311918683</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
@@ -18356,15 +18356,15 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J245">
-        <v>2277</v>
+        <v>3746</v>
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918683</t>
+          <t xml:space="preserve">311918682</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
@@ -18431,11 +18431,11 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J246">
-        <v>3746</v>
+        <v>646</v>
       </c>
       <c r="K246" t="inlineStr">
         <is>
@@ -18491,7 +18491,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lerpøtvej 55</t>
+          <t xml:space="preserve">Lerpøtvej 55A</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
@@ -18506,11 +18506,11 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J247">
-        <v>646</v>
+        <v>956</v>
       </c>
       <c r="K247" t="inlineStr">
         <is>
@@ -18566,40 +18566,40 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lerpøtvej 55A</t>
+          <t xml:space="preserve">Jernbanegade 14</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6870</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t xml:space="preserve">5756829</t>
+          <t xml:space="preserve">8290907</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J248">
-        <v>956</v>
+        <v>341</v>
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918682</t>
+          <t xml:space="preserve">311931080</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Danske Bygningsrådgivere ApS</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-12</t>
+          <t xml:space="preserve">2036-10-09</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
